--- a/practice/answers/s1_q22.xlsx
+++ b/practice/answers/s1_q22.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Answer" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Answer" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,45 +28,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="004A7C59"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="0024302A"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Consolas"/>
-      <color rgb="002F5D46"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="005C6B62"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -75,12 +40,27 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6EFD9"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="004A7C59"/>
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00CFE2F3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D2E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,32 +79,22 @@
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,192 +460,252 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>A threshold the formula reads rather than holds</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>COUNTIF can point its criterion at a cell if you join the operator on with &amp;. Then changing the threshold is one edit, not several.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1"/>
-    <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Threshold (bu/ac)</t>
+          <t>Bin</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Yield (bu/ac)</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Threshold</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bin A</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bin B</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>44.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bin C</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1"/>
-    <row r="6" ht="18" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>Bin</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Yield (bu/ac)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Bin A</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>58.2</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>Bin B</t>
-        </is>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>44.7</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Bin C</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n">
         <v>61.9</v>
       </c>
     </row>
-    <row r="10" ht="18" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Bin D</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B5" s="4" t="n">
         <v>39.4</v>
       </c>
     </row>
-    <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
+    <row r="6">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Bin E</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n">
+      <c r="B6" s="4" t="n">
         <v>55</v>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Bin F</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B7" s="4" t="n">
         <v>47.8</v>
       </c>
     </row>
-    <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Bin G</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n">
+      <c r="B8" s="4" t="n">
         <v>63.1</v>
       </c>
     </row>
-    <row r="14" ht="18" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Bin H</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B9" s="4" t="n">
         <v>41.2</v>
       </c>
     </row>
-    <row r="15" ht="18" customHeight="1"/>
-    <row r="16" ht="18" customHeight="1">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>Count above the threshold</t>
-        </is>
-      </c>
-      <c r="C16" s="9">
-        <f>COUNTIF(B7:B14,"&gt;"&amp;$B$4)</f>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Bins above threshold</t>
+        </is>
+      </c>
+      <c r="B11" s="5">
+        <f>COUNTIF(B2:B9,"&gt;"&amp;$D$1)</f>
         <v/>
       </c>
-      <c r="D16" s="10">
-        <f>_xlfn.FORMULATEXT(C16)</f>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Fraction above</t>
+        </is>
+      </c>
+      <c r="B12" s="7">
+        <f>COUNTIF(B2:B9,"&gt;"&amp;$D$1)/COUNT(B2:B9)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="18" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>Fraction above</t>
-        </is>
-      </c>
-      <c r="C17" s="11">
-        <f>COUNTIF(B7:B14,"&gt;"&amp;$B$4)/COUNT(B7:B14)</f>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Average of all bins</t>
+        </is>
+      </c>
+      <c r="B13" s="9">
+        <f>AVERAGE(B2:B9)</f>
         <v/>
       </c>
-      <c r="D17" s="10">
-        <f>_xlfn.FORMULATEXT(C17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>Average of all bins</t>
-        </is>
-      </c>
-      <c r="C18" s="12">
-        <f>AVERAGE(B7:B14)</f>
-        <v/>
-      </c>
-      <c r="D18" s="10">
-        <f>_xlfn.FORMULATEXT(C18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" ht="18" customHeight="1"/>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Four of eight at a threshold of 50, three at 55. The &amp; is what makes it read the cell: anything inside quotation marks is treated as literal text, so "&gt;$B$4" would look for that string rather than a comparison.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="18" customHeight="1"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>With the threshold cell changed to 55.0, the count becomes 3 (Bins A, C and G) and the fraction 38% -- both formulas point at the threshold cell, so the one edit reruns them. The sheet here keeps the original 50.0.</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>With "&gt;50" the threshold is locked inside the formula text, so part (d) would mean editing the formula itself rather than one cell -- and every other formula using the threshold would need the same edit.</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="13" t="n"/>
+      <c r="E19" s="13" t="n"/>
+      <c r="F19" s="13" t="n"/>
+      <c r="G19" s="13" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="13" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="13" t="n"/>
+      <c r="E20" s="13" t="n"/>
+      <c r="F20" s="13" t="n"/>
+      <c r="G20" s="13" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="13" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="13" t="n"/>
+      <c r="E21" s="13" t="n"/>
+      <c r="F21" s="13" t="n"/>
+      <c r="G21" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Part (a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Part (b)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Part (c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Part (d)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Part (e)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A19:G21"/>
+    <mergeCell ref="A15:G17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
